--- a/data_comp.xlsx
+++ b/data_comp.xlsx
@@ -32,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -43,12 +43,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
         <bgColor rgb="FFD9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -78,7 +72,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -472,112 +465,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) FROM DBT_POC.PUBLIC.FACT_ORDERS;</t>
+          <t>SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS;</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-- INVALID SQL
--- Execution failed on sql 'SELECT COUNT(*) FROM DBT_POC.PUBLIC.STG_ORDERS;': 002003 (42S02): SQL compilation error:
-Object 'DBT_POC.PUBLIC.STG_ORDERS' does not exist or not authorized.
-SELECT COUNT(*) FROM DBT_POC.PUBLIC.STG_ORDERS;</t>
+          <t>SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.STG_ORDERS;</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>001003 (42000): SQL compilation error:
-syntax error line 1 at position 0 unexpected 'Object'.</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) FROM FACT_ORDERS WHERE ORDER_STATUS = 'Completed';</t>
+          <t>SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS WHERE ORDER_STATUS = 'Completed';</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-- INVALID SQL
--- Execution failed on sql 'SELECT COUNT(*) FROM DBT_POC.PUBLIC.STG_ORDERS;': 002003 (42S02): SQL compilation error:
-Object 'DBT_POC.PUBLIC.STG_ORDERS' does not exist or not authorized.
-SELECT COUNT(*) FROM DBT_POC.PUBLIC.STG_ORDERS;</t>
+          <t>SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.STG_ORDERS;</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>001003 (42000): SQL compilation error:
-syntax error line 1 at position 0 unexpected 'Object'.</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SELECT COUNT(FACT_ORDERS.ORDER_ID) FROM FACT_ORDERS WHERE FACT_ORDERS.ORDER_STATUS = 'completed' AND FACT_ORDERS.ORDER_ID IS NULL;</t>
+          <t>SELECT COUNT(FACT_ORDERS.ORDER_ID) FROM FACT_ORDERS WHERE FACT_ORDERS.ORDER_STATUS = 'Completed' AND FACT_ORDERS.PAYMENT_METHOD IS NULL;</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SELECT * FROM (SELECT 'FACT_ORDERS' AS "TABLE", 'ORDER_ID' AS "COLUMN" UNION SELECT 'FACT_ORDERS', 'ORDER_DATE_KEY' UNION SELECT 'FACT_ORDERS', 'CUSTOMER_KEY' UNION SELECT 'FACT_ORDERS', 'CHANNEL_KEY' UNION SELECT 'FACT_ORDERS', 'PROMO_KEY' UNION SELECT 'FACT_ORDERS', 'ORDER_STATUS' UNION SELECT 'FACT_ORDERS', 'PAYMENT_METHOD' UNION SELECT 'FACT_ORDER_ITEMS', 'ORDER_ID' UNION SELECT 'FACT_ORDER_ITEMS', 'PRODUCT_KEY' UNION SELECT 'FACT_ORDER_ITEMS', 'QUANTITY' UNION SELECT 'FACT_ORDER_ITEMS', 'UNIT_PRICE' UNION SELECT 'FACT_ORDER_ITEMS', 'DISCOUNT_AMOUNT' UNION SELECT 'FACT_ORDER_ITEMS', 'COST_AMOUNT') AS t WHERE NOT EXISTS (SELECT 1 FROM DBT_POC.PUBLIC.FACT_ORDERS WHERE t."COLUMN" IS NULL UNION SELECT 1 FROM DBT_POC.PUBLIC.FACT_ORDER_ITEMS WHERE t."COLUMN" IS NULL);</t>
+          <t>SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.STG_ORDERS WHERE ORDER_ID IS NULL OR ORDER_DATE_KEY IS NULL OR CUSTOMER_KEY IS NULL OR CHANNEL_KEY IS NULL OR PROMO_KEY IS NULL OR ORDER_STATUS IS NULL OR MODE IS NULL;</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) FROM (SELECT ORDER_ID FROM FACT_ORDERS WHERE ORDER_STATUS = 'completed' GROUP BY ORDER_ID HAVING COUNT(*) &gt; 1) AS _q_0;</t>
+          <t>SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS WHERE FACT_ORDERS.ORDER_STATUS = 'Completed';</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) FROM (SELECT ORDER_ID FROM FACT_ORDER_ITEMS GROUP BY ORDER_ID HAVING COUNT(ORDER_ID) &gt; 1) AS _q_0;</t>
+          <t>SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.STG_ORDERS GROUP BY ORDER_ID HAVING COUNT(*) &gt; 1;</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>'ROW_ID'</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SELECT * FROM FACT_ORDERS WHERE ORDER_STATUS = 'Completed';</t>
+          <t>SELECT * FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS WHERE ORDER_STATUS = 'Completed';</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-- INVALID SQL
--- Execution failed on sql 'SELECT * FROM DBT_POC.PUBLIC.STG_ORDERS;': 002003 (42S02): SQL compilation error:
-Object 'DBT_POC.PUBLIC.STG_ORDERS' does not exist or not authorized.
-SELECT * FROM DBT_POC.PUBLIC.STG_ORDERS;</t>
+          <t>SELECT STG_ORDERS.ORDER_ID, STG_ORDERS.ORDER_DATE_KEY, STG_ORDERS.CUSTOMER_KEY, STG_ORDERS.CHANNEL_KEY, STG_ORDERS.PROMO_KEY, STG_ORDERS.ORDER_STATUS, STG_ORDERS.MODE FROM DBT_POC.DBT_SCHEMA.STG_ORDERS;</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>001003 (42000): SQL compilation error:
-syntax error line 1 at position 0 unexpected 'Object'.</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -589,7 +560,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SELECT COUNT(FACT_ORDERS.ORDER_ID) FROM FACT_ORDERS GROUP BY FACT_ORDERS.ORDER_ID HAVING COUNT(FACT_ORDERS.ORDER_ID) &gt; 1;</t>
+          <t>SELECT COUNT(STG_ORDERS.ORDER_ID) FROM STG_ORDERS GROUP BY STG_ORDERS.ORDER_ID HAVING COUNT(STG_ORDERS.ORDER_ID) &gt; 1;</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -606,17 +577,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SELECT SUM(FACT_ORDER_ITEMS.UNIT_PRICE * FACT_ORDER_ITEMS.QUANTITY - FACT_ORDER_ITEMS.DISCOUNT_AMOUNT) AS revenue FROM FACT_ORDER_ITEMS INNER JOIN FACT_ORDERS ON FACT_ORDER_ITEMS.ORDER_ID = FACT_ORDERS.ORDER_ID WHERE FACT_ORDERS.ORDER_DATE_KEY = FACT_ORDERS.ORDER_DATE_KEY;</t>
+          <t>-- INVALID SQL
+-- Execution failed on sql 'SELECT SUM(FACT_ORDER_ITEMS.UNIT_PRICE * FACT_ORDER_ITEMS.QUANTITY) AS DAILY_REVENUE FROM FACT_ORDER_ITEMS INNER JOIN FACT_ORDERS ON FACT_ORDER_ITEMS.ORDER_ID = FACT_ORDERS.ORDER_ID WHERE FACT_ORDERS.ORDER_DATE_KEY = DAILY_REVENUE.DATE_VALUE;': 000904 (42000): SQL compilation error: error line 1 at position 217
+invalid identifier 'DAILY_REVENUE.DATE_VALUE'
+SELECT SUM(FACT_ORDER_ITEMS.UNIT_PRICE * FACT_ORDER_ITEMS.QUANTITY) AS DAILY_REVENUE FROM FACT_ORDER_ITEMS INNER JOIN FACT_ORDERS ON FACT_ORDER_ITEMS.ORDER_ID = FACT_ORDERS.ORDER_ID WHERE FACT_ORDERS.ORDER_DATE_KEY = DAILY_REVENUE.DATE_VALUE;</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SELECT SUM(FACT_ORDER_ITEMS.UNIT_PRICE * FACT_ORDER_ITEMS.QUANTITY - FACT_ORDER_ITEMS.DISCOUNT_AMOUNT) AS daily_revenue FROM FACT_ORDER_ITEMS WHERE FACT_ORDER_ITEMS.ORDER_ID IN (SELECT FACT_ORDERS.ORDER_ID FROM FACT_ORDERS);</t>
+          <t>SELECT SUM(DAILY_REVENUE.DAILY_REVENUE) FROM DAILY_REVENUE;</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>001003 (42000): SQL compilation error:
+syntax error line 1 at position 0 unexpected 'invalid'.</t>
         </is>
       </c>
     </row>
@@ -631,13 +611,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>TEST 3</t>
+          <t>TEST 4</t>
         </is>
       </c>
     </row>
@@ -649,7 +629,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>COUNT(FACT_ORDERS.ORDER_ID)</t>
+          <t>COUNT(*)</t>
         </is>
       </c>
     </row>
@@ -659,14 +639,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TEST 4</t>
+          <t>TEST 6</t>
         </is>
       </c>
     </row>
@@ -678,7 +658,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>COUNT(*)</t>
+          <t>COUNT(FACT_ORDERS.ORDER_ID)</t>
         </is>
       </c>
     </row>
@@ -688,42 +668,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TEST 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>ROW_ID</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>COUNT(FACT_ORDERS.ORDER_ID)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
           <t>3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A9:B9"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A5:B5"/>
   </mergeCells>
@@ -737,192 +687,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>TEST 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>ROW_ID</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>COUNT(FACT_ORDERS.ORDER_ID)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>FACT_ORDERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>FACT_ORDERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FACT_ORDERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>FACT_ORDERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FACT_ORDERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>FACT_ORDERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>FACT_ORDERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>FACT_ORDER_ITEMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>FACT_ORDER_ITEMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>FACT_ORDER_ITEMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FACT_ORDER_ITEMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>FACT_ORDER_ITEMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>FACT_ORDER_ITEMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TEST 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ROW_ID</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>COUNT(*)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>INFO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A17:B17"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -933,304 +708,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>TEST 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Row_number</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>COUNT(FACT_ORDERS.ORDER_ID)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SRC</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>FACT_ORDERS</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FACT_ORDERS</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ONLY_IN_TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>FACT_ORDERS</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ONLY_IN_TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FACT_ORDERS</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ONLY_IN_TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>FACT_ORDERS</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ONLY_IN_TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>FACT_ORDERS</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ONLY_IN_TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>FACT_ORDERS</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ONLY_IN_TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>FACT_ORDER_ITEMS</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ONLY_IN_TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>FACT_ORDER_ITEMS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ONLY_IN_TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FACT_ORDER_ITEMS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ONLY_IN_TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>FACT_ORDER_ITEMS</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ONLY_IN_TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>FACT_ORDER_ITEMS</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ONLY_IN_TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>FACT_ORDER_ITEMS</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ONLY_IN_TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TEST 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Row_number</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>COUNT(*)</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SRC</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>TGT</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>INFO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A18:C18"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data_comp.xlsx
+++ b/data_comp.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,7 +516,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS WHERE FACT_ORDERS.ORDER_STATUS = 'Completed';</t>
+          <t>SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS WHERE ORDER_STATUS = 'Completed';</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -577,26 +577,49 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>SELECT SUM(FACT_ORDER_ITEMS.UNIT_PRICE * FACT_ORDER_ITEMS.QUANTITY) - SUM(FACT_ORDER_ITEMS.DISCOUNT_AMOUNT) FROM FACT_ORDER_ITEMS;</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SELECT SUM(DAILY_REVENUE.DAILY_REV) FROM DAILY_REVENUE;</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>000904 (42000): SQL compilation error: error line 1 at position 11
+invalid identifier 'DAILY_REVENUE.DAILY_REV'</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SELECT DIM_CUSTOMER.CUSTOMER_KEY, DIM_CUSTOMER.CUSTOMER_ID, DIM_CUSTOMER.CUSTOMER_NAME, DIM_CUSTOMER.SEGMENT, DIM_GEOGRAPHY.CITY, DIM_GEOGRAPHY.STATE_REGION, DIM_GEOGRAPHY.COUNTRY FROM DIM_CUSTOMER INNER JOIN DIM_GEOGRAPHY ON DIM_CUSTOMER.GEO_KEY = DIM_GEOGRAPHY.GEO_KEY;</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>-- INVALID SQL
--- Execution failed on sql 'SELECT SUM(FACT_ORDER_ITEMS.UNIT_PRICE * FACT_ORDER_ITEMS.QUANTITY) AS DAILY_REVENUE FROM FACT_ORDER_ITEMS INNER JOIN FACT_ORDERS ON FACT_ORDER_ITEMS.ORDER_ID = FACT_ORDERS.ORDER_ID WHERE FACT_ORDERS.ORDER_DATE_KEY = DAILY_REVENUE.DATE_VALUE;': 000904 (42000): SQL compilation error: error line 1 at position 217
-invalid identifier 'DAILY_REVENUE.DATE_VALUE'
-SELECT SUM(FACT_ORDER_ITEMS.UNIT_PRICE * FACT_ORDER_ITEMS.QUANTITY) AS DAILY_REVENUE FROM FACT_ORDER_ITEMS INNER JOIN FACT_ORDERS ON FACT_ORDER_ITEMS.ORDER_ID = FACT_ORDERS.ORDER_ID WHERE FACT_ORDERS.ORDER_DATE_KEY = DAILY_REVENUE.DATE_VALUE;</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SELECT SUM(DAILY_REVENUE.DAILY_REVENUE) FROM DAILY_REVENUE;</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+-- Execution failed on sql 'SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.DIM_CUSTOMER_ENR;': 002003 (42S02): SQL compilation error:
+Object 'DBT_POC.DBT_SCHEMA.DIM_CUSTOMER_ENR' does not exist or not authorized.
+SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.DIM_CUSTOMER_ENR;</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>001003 (42000): SQL compilation error:
-syntax error line 1 at position 0 unexpected 'invalid'.</t>
+syntax error line 1 at position 0 unexpected 'Object'.</t>
         </is>
       </c>
     </row>

--- a/data_comp.xlsx
+++ b/data_comp.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,73 +516,71 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS WHERE ORDER_STATUS = 'Completed';</t>
+          <t>SELECT * FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS WHERE ORDER_STATUS = 'Completed';</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.STG_ORDERS GROUP BY ORDER_ID HAVING COUNT(*) &gt; 1;</t>
+          <t>SELECT STG_ORDERS.ORDER_ID, STG_ORDERS.ORDER_DATE_KEY, STG_ORDERS.CUSTOMER_KEY, STG_ORDERS.CHANNEL_KEY, STG_ORDERS.PROMO_KEY, STG_ORDERS.ORDER_STATUS, STG_ORDERS.MODE FROM DBT_POC.DBT_SCHEMA.STG_ORDERS;</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>'ROW_ID'</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SELECT * FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS WHERE ORDER_STATUS = 'Completed';</t>
+          <t>SELECT COUNT(FACT_ORDERS.ORDER_ID) FROM FACT_ORDERS WHERE FACT_ORDERS.ORDER_STATUS = 'Completed';</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SELECT STG_ORDERS.ORDER_ID, STG_ORDERS.ORDER_DATE_KEY, STG_ORDERS.CUSTOMER_KEY, STG_ORDERS.CHANNEL_KEY, STG_ORDERS.PROMO_KEY, STG_ORDERS.ORDER_STATUS, STG_ORDERS.MODE FROM DBT_POC.DBT_SCHEMA.STG_ORDERS;</t>
+          <t>SELECT COUNT(STG_ORDERS.ORDER_ID) FROM STG_ORDERS GROUP BY STG_ORDERS.ORDER_ID HAVING COUNT(STG_ORDERS.ORDER_ID) &gt; 1;</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>'ROW_ID'</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SELECT COUNT(FACT_ORDERS.ORDER_ID) FROM FACT_ORDERS WHERE FACT_ORDERS.ORDER_STATUS = 'Completed';</t>
+          <t>SELECT SUM(FACT_ORDER_ITEMS.UNIT_PRICE * FACT_ORDER_ITEMS.QUANTITY) - SUM(FACT_ORDER_ITEMS.DISCOUNT_AMOUNT) FROM FACT_ORDER_ITEMS INNER JOIN FACT_ORDERS ON FACT_ORDER_ITEMS.ORDER_ID = FACT_ORDERS.ORDER_ID;</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SELECT COUNT(STG_ORDERS.ORDER_ID) FROM STG_ORDERS GROUP BY STG_ORDERS.ORDER_ID HAVING COUNT(STG_ORDERS.ORDER_ID) &gt; 1;</t>
+          <t>SELECT SUM(DAILY_REVENUE.DAILY_REVENUE) FROM DAILY_REVENUE;</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>'ROW_ID'</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SELECT SUM(FACT_ORDER_ITEMS.UNIT_PRICE * FACT_ORDER_ITEMS.QUANTITY) - SUM(FACT_ORDER_ITEMS.DISCOUNT_AMOUNT) FROM FACT_ORDER_ITEMS;</t>
+          <t>SELECT DIM_CUSTOMER.CUSTOMER_KEY, DIM_CUSTOMER.CUSTOMER_ID, DIM_CUSTOMER.CUSTOMER_NAME, DIM_CUSTOMER.SEGMENT, DIM_GEOGRAPHY.CITY, DIM_GEOGRAPHY.STATE_REGION, DIM_GEOGRAPHY.COUNTRY FROM DIM_CUSTOMER INNER JOIN DIM_GEOGRAPHY ON DIM_CUSTOMER.GEO_KEY = DIM_GEOGRAPHY.GEO_KEY;</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SELECT SUM(DAILY_REVENUE.DAILY_REV) FROM DAILY_REVENUE;</t>
+          <t>-- INVALID SQL
+-- Execution failed on sql 'SELECT * FROM DBT_POC.DBT_SCHEMA.DIM_CUSTOMER_ENR WHERE CUSTOMER_KEY IN (SELECT CUSTOMER_KEY FROM DBT_POC.DBT_SCHEMA.DIM_CUSTOMER);': 002003 (42S02): SQL compilation error:
+Object 'DBT_POC.DBT_SCHEMA.DIM_CUSTOMER_ENR' does not exist or not authorized.
+SELECT * FROM DBT_POC.DBT_SCHEMA.DIM_CUSTOMER_ENR WHERE CUSTOMER_KEY IN (SELECT CUSTOMER_KEY FROM DBT_POC.DBT_SCHEMA.DIM_CUSTOMER);</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -591,32 +589,6 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>000904 (42000): SQL compilation error: error line 1 at position 11
-invalid identifier 'DAILY_REVENUE.DAILY_REV'</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SELECT DIM_CUSTOMER.CUSTOMER_KEY, DIM_CUSTOMER.CUSTOMER_ID, DIM_CUSTOMER.CUSTOMER_NAME, DIM_CUSTOMER.SEGMENT, DIM_GEOGRAPHY.CITY, DIM_GEOGRAPHY.STATE_REGION, DIM_GEOGRAPHY.COUNTRY FROM DIM_CUSTOMER INNER JOIN DIM_GEOGRAPHY ON DIM_CUSTOMER.GEO_KEY = DIM_GEOGRAPHY.GEO_KEY;</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>-- INVALID SQL
--- Execution failed on sql 'SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.DIM_CUSTOMER_ENR;': 002003 (42S02): SQL compilation error:
-Object 'DBT_POC.DBT_SCHEMA.DIM_CUSTOMER_ENR' does not exist or not authorized.
-SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.DIM_CUSTOMER_ENR;</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
         <is>
           <t>001003 (42000): SQL compilation error:
 syntax error line 1 at position 0 unexpected 'Object'.</t>
@@ -634,13 +606,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>TEST 4</t>
+          <t>TEST 5</t>
         </is>
       </c>
     </row>
@@ -652,7 +624,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>COUNT(*)</t>
+          <t>COUNT(FACT_ORDERS.ORDER_ID)</t>
         </is>
       </c>
     </row>
@@ -666,39 +638,9 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TEST 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ROW_ID</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>COUNT(FACT_ORDERS.ORDER_ID)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_comp.xlsx
+++ b/data_comp.xlsx
@@ -565,7 +565,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>000904 (42000): SQL compilation error: error line 1 at position 11
+invalid identifier 'DAILY_REVENUE.DAILY_REVENUE'</t>
         </is>
       </c>
     </row>

--- a/data_comp.xlsx
+++ b/data_comp.xlsx
@@ -32,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
         <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -72,6 +78,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -521,7 +528,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SELECT STG_ORDERS.ORDER_ID, STG_ORDERS.ORDER_DATE_KEY, STG_ORDERS.CUSTOMER_KEY, STG_ORDERS.CHANNEL_KEY, STG_ORDERS.PROMO_KEY, STG_ORDERS.ORDER_STATUS, STG_ORDERS.MODE FROM DBT_POC.DBT_SCHEMA.STG_ORDERS;</t>
+          <t>SELECT STG_ORDERS.ORDER_ID, STG_ORDERS.ORDER_DATE_KEY, STG_ORDERS.CUSTOMER_KEY, STG_ORDERS.CHANNEL_KEY, STG_ORDERS.PROMO_KEY, STG_ORDERS.ORDER_STATUS, STG_ORDERS.MODE FROM DBT_SCHEMA.STG_ORDERS WHERE STG_ORDERS.ORDER_STATUS = 'Completed';</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -533,12 +540,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SELECT COUNT(FACT_ORDERS.ORDER_ID) FROM FACT_ORDERS WHERE FACT_ORDERS.ORDER_STATUS = 'Completed';</t>
+          <t>SELECT COUNT(FACT_ORDERS.ORDER_ID) FROM FACT_ORDERS WHERE FACT_ORDERS.ORDER_STATUS = 'Completed' GROUP BY FACT_ORDERS.ORDER_ID HAVING COUNT(FACT_ORDERS.ORDER_ID) &gt; 1;</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SELECT COUNT(STG_ORDERS.ORDER_ID) FROM STG_ORDERS GROUP BY STG_ORDERS.ORDER_ID HAVING COUNT(STG_ORDERS.ORDER_ID) &gt; 1;</t>
+          <t>SELECT STG_ORDERS.ORDER_ID FROM STG_ORDERS GROUP BY STG_ORDERS.ORDER_ID HAVING COUNT(*) &gt; 1;</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -548,7 +555,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>'ROW_ID'</t>
+          <t>'EXTRA_IN_SRC'</t>
         </is>
       </c>
     </row>
@@ -560,7 +567,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SELECT SUM(DAILY_REVENUE.DAILY_REVENUE) FROM DAILY_REVENUE;</t>
+          <t>SELECT SUM(DAILY_REVENUE.DAILY_REV) FROM DAILY_REVENUE;</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -571,7 +578,7 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>000904 (42000): SQL compilation error: error line 1 at position 11
-invalid identifier 'DAILY_REVENUE.DAILY_REVENUE'</t>
+invalid identifier 'DAILY_REVENUE.DAILY_REV'</t>
         </is>
       </c>
     </row>
@@ -583,21 +590,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-- INVALID SQL
--- Execution failed on sql 'SELECT * FROM DBT_POC.DBT_SCHEMA.DIM_CUSTOMER_ENR WHERE CUSTOMER_KEY IN (SELECT CUSTOMER_KEY FROM DBT_POC.DBT_SCHEMA.DIM_CUSTOMER);': 002003 (42S02): SQL compilation error:
-Object 'DBT_POC.DBT_SCHEMA.DIM_CUSTOMER_ENR' does not exist or not authorized.
-SELECT * FROM DBT_POC.DBT_SCHEMA.DIM_CUSTOMER_ENR WHERE CUSTOMER_KEY IN (SELECT CUSTOMER_KEY FROM DBT_POC.DBT_SCHEMA.DIM_CUSTOMER);</t>
+          <t>SELECT * FROM DBT_POC.DBT_SCHEMA.DIM_CUSTOMER_ENR;</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>001003 (42000): SQL compilation error:
-syntax error line 1 at position 0 unexpected 'Object'.</t>
         </is>
       </c>
     </row>
@@ -612,13 +610,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>TEST 5</t>
+          <t>TEST 7</t>
         </is>
       </c>
     </row>
@@ -630,7 +628,37 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>COUNT(FACT_ORDERS.ORDER_ID)</t>
+          <t>CUSTOMER_KEY</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ID</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>CUSTOMER_NAME</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>SEGMENT</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>CITY</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>STATE_REGION</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>COUNTRY</t>
         </is>
       </c>
     </row>
@@ -640,13 +668,83 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Akash Kumar</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ravi Iyer</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>India</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -658,17 +756,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>INFO</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>TEST 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ROW_ID</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>CUSTOMER_KEY</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ID</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>CUSTOMER_NAME</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>SEGMENT</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>CITY</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>STATE_REGION</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>COUNTRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Akash Kumar</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ravi Iyer</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>India</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -679,17 +902,248 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>INFO</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>TEST 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Row_number</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>CUSTOMER_KEY</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ID</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>CUSTOMER_NAME</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>SEGMENT</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>CITY</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>STATE_REGION</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>COUNTRY</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Akash Kumar</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SRC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Akash Kumar</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ravi Iyer</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SRC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ravi Iyer</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>TGT</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data_comp.xlsx
+++ b/data_comp.xlsx
@@ -567,18 +567,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SELECT SUM(DAILY_REVENUE.DAILY_REV) FROM DAILY_REVENUE;</t>
+          <t>SELECT SUM(DAILY_REVENUE.DAILY_REVENUE) FROM DAILY_REVENUE;</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>000904 (42000): SQL compilation error: error line 1 at position 11
-invalid identifier 'DAILY_REVENUE.DAILY_REV'</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>

--- a/data_comp.xlsx
+++ b/data_comp.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,7 +540,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SELECT COUNT(FACT_ORDERS.ORDER_ID) FROM FACT_ORDERS WHERE FACT_ORDERS.ORDER_STATUS = 'Completed' GROUP BY FACT_ORDERS.ORDER_ID HAVING COUNT(FACT_ORDERS.ORDER_ID) &gt; 1;</t>
+          <t>SELECT FACT_ORDERS.ORDER_ID FROM FACT_ORDERS WHERE FACT_ORDERS.ORDER_STATUS = 'Completed' GROUP BY FACT_ORDERS.ORDER_ID HAVING COUNT(FACT_ORDERS.ORDER_ID) &gt; 1;</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,6 +588,62 @@
         </is>
       </c>
       <c r="C8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SELECT FACT_ORDERS.ORDER_ID FROM FACT_ORDERS GROUP BY FACT_ORDERS.ORDER_ID HAVING COUNT(FACT_ORDERS.ORDER_ID) &gt; 1;</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SELECT STG_ORDERS.ORDER_ID FROM STG_ORDERS GROUP BY STG_ORDERS.ORDER_ID HAVING COUNT(*) &gt; 1;</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>'EXTRA_IN_SRC'</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SELECT SUM(FACT_ORDER_ITEMS.QUANTITY), COUNT(FACT_ORDERS.ORDER_ID) FROM FACT_ORDERS INNER JOIN FACT_ORDER_ITEMS ON FACT_ORDERS.ORDER_ID = FACT_ORDER_ITEMS.ORDER_ID WHERE FACT_ORDERS.ORDER_STATUS = 'Completed';</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SELECT SUM(CUSTOMER_SALES.TOTAL_SPENT), SUM(CUSTOMER_SALES.TOTAL_ORDERS) FROM CUSTOMER_SALES;</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SELECT SUM(FACT_ORDER_ITEMS.UNIT_PRICE * FACT_ORDER_ITEMS.QUANTITY) AS GROSS_REVENUE, SUM(FACT_ORDER_ITEMS.DISCOUNT_AMOUNT) AS TOTAL_DISCOUNT, SUM(FACT_ORDER_ITEMS.UNIT_PRICE * FACT_ORDER_ITEMS.QUANTITY - FACT_ORDER_ITEMS.DISCOUNT_AMOUNT) AS NET_REVENUE FROM FACT_ORDER_ITEMS;</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SELECT ORDER_REVENUE.GROSS_REVENUE, ORDER_REVENUE.TOTAL_DISCOUNT, ORDER_REVENUE.NET_REVENUE FROM DBT_SCHEMA.ORDER_REVENUE;</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -604,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -736,8 +792,98 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TEST 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ROW_ID</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>SUM(FACT_ORDER_ITEMS.QUANTITY)</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>COUNT(FACT_ORDERS.ORDER_ID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TEST 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ROW_ID</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>GROSS_REVENUE</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL_DISCOUNT</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>NET_REVENUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15500.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1520.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>13980.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -750,7 +896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,8 +1028,138 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TEST 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ROW_ID</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>SUM(FACT_ORDER_ITEMS.QUANTITY)</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>COUNT(FACT_ORDERS.ORDER_ID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13980.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TEST 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ROW_ID</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>GROSS_REVENUE</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL_DISCOUNT</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>NET_REVENUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4000.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4300.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>860.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3440.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7200.00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>660.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6540.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -896,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1134,9 +1410,216 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TEST 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Row_number</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>SUM(FACT_ORDER_ITEMS.QUANTITY)</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>COUNT(FACT_ORDERS.ORDER_ID)</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SRC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13980.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TEST 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Row_number</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>GROSS_REVENUE</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL_DISCOUNT</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>NET_REVENUE</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>15500.00</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>1520.00</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>13980.00</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SRC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>4000.00</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>4000.00</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4300.00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>860.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3440.00</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ONLY_IN_TGT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7200.00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>660.00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6540.00</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ONLY_IN_TGT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_comp.xlsx
+++ b/data_comp.xlsx
@@ -550,12 +550,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>'EXTRA_IN_SRC'</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -606,12 +601,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>'EXTRA_IN_SRC'</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>

--- a/data_comp.xlsx
+++ b/data_comp.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="data_comp" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="A_MINUS_B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="B_MINUS_A" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="mismatch" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mismatch in source" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Mismatch in target" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Consolidated" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data_comp.xlsx
+++ b/data_comp.xlsx
@@ -516,7 +516,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>000904 (42000): SQL compilation error: error line 1 at position 195
+invalid identifier 'MODE'</t>
         </is>
       </c>
     </row>
@@ -533,7 +539,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>000904 (42000): SQL compilation error: error line 1 at position 151
+invalid identifier 'STG_ORDERS.MODE'</t>
         </is>
       </c>
     </row>

--- a/data_comp.xlsx
+++ b/data_comp.xlsx
@@ -516,13 +516,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>000904 (42000): SQL compilation error: error line 1 at position 195
-invalid identifier 'MODE'</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -539,13 +533,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>000904 (42000): SQL compilation error: error line 1 at position 151
-invalid identifier 'STG_ORDERS.MODE'</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>

--- a/data_comp.xlsx
+++ b/data_comp.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,58 +506,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SELECT COUNT(FACT_ORDERS.ORDER_ID) FROM FACT_ORDERS WHERE FACT_ORDERS.ORDER_STATUS = 'Completed' AND FACT_ORDERS.PAYMENT_METHOD IS NULL;</t>
+          <t>SELECT dim_product.PRODUCT_NAME, dim_product.BRAND, SUM(fact_order_items.QUANTITY) AS TOTAL_QTY, SUM((fact_order_items.QUANTITY * fact_order_items.UNIT_PRICE) - fact_order_items.DISCOUNT_AMOUNT) AS TOTAL_REVENUE FROM fact_order_items JOIN dim_product ON fact_order_items.PRODUCT_KEY = dim_product.PRODUCT_KEY GROUP BY dim_product.PRODUCT_NAME, dim_product.BRAND ORDER BY TOTAL_REVENUE DESC LIMIT 1;</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) FROM DBT_POC.DBT_SCHEMA.STG_ORDERS WHERE ORDER_ID IS NULL OR ORDER_DATE_KEY IS NULL OR CUSTOMER_KEY IS NULL OR CHANNEL_KEY IS NULL OR PROMO_KEY IS NULL OR ORDER_STATUS IS NULL OR MODE IS NULL;</t>
+          <t>SELECT PRODUCT_SALES.PRODUCT_NAME, PRODUCT_SALES.BRAND, PRODUCT_SALES.TOTAL_QTY, PRODUCT_SALES.TOTAL_REVENUE FROM PRODUCT_SALES ORDER BY PRODUCT_SALES.TOTAL_REVENUE DESC LIMIT 1;</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>000904 (42000): SQL compilation error: error line 1 at position 195
-invalid identifier 'MODE'</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SELECT * FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS WHERE ORDER_STATUS = 'Completed';</t>
+          <t>SELECT DIM_CUSTOMER.CUSTOMER_KEY, DIM_CUSTOMER.CUSTOMER_ID, DIM_CUSTOMER.CUSTOMER_NAME, DIM_CUSTOMER.SEGMENT, DIM_GEOGRAPHY.CITY, DIM_GEOGRAPHY.STATE_REGION, DIM_GEOGRAPHY.COUNTRY FROM DIM_CUSTOMER INNER JOIN DIM_GEOGRAPHY ON DIM_CUSTOMER.GEO_KEY = DIM_GEOGRAPHY.GEO_KEY;</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SELECT STG_ORDERS.ORDER_ID, STG_ORDERS.ORDER_DATE_KEY, STG_ORDERS.CUSTOMER_KEY, STG_ORDERS.CHANNEL_KEY, STG_ORDERS.PROMO_KEY, STG_ORDERS.ORDER_STATUS, STG_ORDERS.MODE FROM DBT_SCHEMA.STG_ORDERS WHERE STG_ORDERS.ORDER_STATUS = 'Completed';</t>
+          <t>SELECT * FROM DBT_SCHEMA.DIM_CUSTOMER_ENR;</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>000904 (42000): SQL compilation error: error line 1 at position 151
-invalid identifier 'STG_ORDERS.MODE'</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SELECT FACT_ORDERS.ORDER_ID FROM FACT_ORDERS WHERE FACT_ORDERS.ORDER_STATUS = 'Completed' GROUP BY FACT_ORDERS.ORDER_ID HAVING COUNT(FACT_ORDERS.ORDER_ID) &gt; 1;</t>
+          <t>SELECT c.CUSTOMER_NAME, c.SEGMENT, COUNT(DISTINCT o.ORDER_ID) AS TOTAL_ORDERS, SUM((oi.QUANTITY * oi.UNIT_PRICE) - oi.DISCOUNT_AMOUNT) AS TOTAL_SPENT FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS o JOIN DBT_POC.DBT_SCHEMA.FACT_ORDER_ITEMS oi ON o.ORDER_ID = oi.ORDER_ID JOIN DBT_POC.DBT_SCHEMA.DIM_CUSTOMER c ON o.CUSTOMER_KEY = c.CUSTOMER_KEY GROUP BY c.CUSTOMER_NAME, c.SEGMENT;</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SELECT STG_ORDERS.ORDER_ID FROM STG_ORDERS GROUP BY STG_ORDERS.ORDER_ID HAVING COUNT(*) &gt; 1;</t>
+          <t>SELECT CUSTOMER_SALES.CUSTOMER_NAME, CUSTOMER_SALES.SEGMENT, CUSTOMER_SALES.TOTAL_ORDERS, CUSTOMER_SALES.TOTAL_SPENT FROM CUSTOMER_SALES;</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -569,12 +557,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SELECT SUM(FACT_ORDER_ITEMS.UNIT_PRICE * FACT_ORDER_ITEMS.QUANTITY) - SUM(FACT_ORDER_ITEMS.DISCOUNT_AMOUNT) FROM FACT_ORDER_ITEMS INNER JOIN FACT_ORDERS ON FACT_ORDER_ITEMS.ORDER_ID = FACT_ORDERS.ORDER_ID;</t>
+          <t>SELECT c.CUSTOMER_NAME, c.SEGMENT, COUNT(DISTINCT o.ORDER_ID) AS TOTAL_ORDERS, SUM((oi.QUANTITY * oi.UNIT_PRICE) - oi.DISCOUNT_AMOUNT) AS TOTAL_SPENT, CASE WHEN SUM((oi.QUANTITY * oi.UNIT_PRICE) - oi.DISCOUNT_AMOUNT) &gt; 1000 THEN 'HIGH' ELSE 'LOW' END AS SPENT_BAND FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS o JOIN DBT_POC.DBT_SCHEMA.FACT_ORDER_ITEMS oi ON o.ORDER_ID = oi.ORDER_ID JOIN DBT_POC.DBT_SCHEMA.DIM_CUSTOMER c ON o.CUSTOMER_KEY = c.CUSTOMER_KEY GROUP BY c.CUSTOMER_NAME, c.SEGMENT;</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SELECT SUM(DAILY_REVENUE.DAILY_REVENUE) FROM DAILY_REVENUE;</t>
+          <t>SELECT CUSTOMER_NAME, SEGMENT, TOTAL_ORDERS, TOTAL_SPENT, CASE WHEN TOTAL_SPENT &gt; 1000 THEN 'HIGH' ELSE 'LOW' END AS SPENT_BAND FROM DBT_SCHEMA.CUSTOMER_SALES;</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -586,12 +574,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SELECT DIM_CUSTOMER.CUSTOMER_KEY, DIM_CUSTOMER.CUSTOMER_ID, DIM_CUSTOMER.CUSTOMER_NAME, DIM_CUSTOMER.SEGMENT, DIM_GEOGRAPHY.CITY, DIM_GEOGRAPHY.STATE_REGION, DIM_GEOGRAPHY.COUNTRY FROM DIM_CUSTOMER INNER JOIN DIM_GEOGRAPHY ON DIM_CUSTOMER.GEO_KEY = DIM_GEOGRAPHY.GEO_KEY;</t>
+          <t>SELECT SUM(oi.QUANTITY * oi.UNIT_PRICE) - SUM(oi.DISCOUNT_AMOUNT) FROM DBT_POC.DBT_SCHEMA.fact_order_items oi WHERE oi.ORDER_ID = 50003;</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SELECT * FROM DBT_POC.DBT_SCHEMA.DIM_CUSTOMER_ENR;</t>
+          <t>-- INVALID SQL
+-- Execution failed on sql 'SELECT SUM(oi.QUANTITY * oi.UNIT_PRICE) - SUM(oi.DISCOUNT_AMOUNT) FROM DBT_POC.DBT_SCHEMA.fact_order_items oi JOIN DBT_POC.DBT_SCHEMA.fact_orders o ON oi.ORDER_ID = o.ORDER_ID WHERE o.ORDER_ID = 'xyz';': 100038 (22018): Numeric value 'xyz' is not recognized
+SELECT SUM(oi.QUANTITY * oi.UNIT_PRICE) - SUM(oi.DISCOUNT_AMOUNT) FROM DBT_POC.DBT_SCHEMA.fact_order_items oi JOIN DBT_POC.DBT_SCHEMA.fact_orders o ON oi.ORDER_ID = o.ORDER_ID WHERE o.ORDER_ID = 'xyz';</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -599,55 +589,9 @@
           <t>FAIL</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SELECT FACT_ORDERS.ORDER_ID FROM FACT_ORDERS GROUP BY FACT_ORDERS.ORDER_ID HAVING COUNT(FACT_ORDERS.ORDER_ID) &gt; 1;</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SELECT STG_ORDERS.ORDER_ID FROM STG_ORDERS GROUP BY STG_ORDERS.ORDER_ID HAVING COUNT(*) &gt; 1;</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SELECT SUM(FACT_ORDER_ITEMS.QUANTITY), COUNT(FACT_ORDERS.ORDER_ID) FROM FACT_ORDERS INNER JOIN FACT_ORDER_ITEMS ON FACT_ORDERS.ORDER_ID = FACT_ORDER_ITEMS.ORDER_ID WHERE FACT_ORDERS.ORDER_STATUS = 'Completed';</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SELECT SUM(CUSTOMER_SALES.TOTAL_SPENT), SUM(CUSTOMER_SALES.TOTAL_ORDERS) FROM CUSTOMER_SALES;</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SELECT SUM(FACT_ORDER_ITEMS.UNIT_PRICE * FACT_ORDER_ITEMS.QUANTITY) AS GROSS_REVENUE, SUM(FACT_ORDER_ITEMS.DISCOUNT_AMOUNT) AS TOTAL_DISCOUNT, SUM(FACT_ORDER_ITEMS.UNIT_PRICE * FACT_ORDER_ITEMS.QUANTITY - FACT_ORDER_ITEMS.DISCOUNT_AMOUNT) AS NET_REVENUE FROM FACT_ORDER_ITEMS;</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SELECT ORDER_REVENUE.GROSS_REVENUE, ORDER_REVENUE.TOTAL_DISCOUNT, ORDER_REVENUE.NET_REVENUE FROM DBT_SCHEMA.ORDER_REVENUE;</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>100038 (22018): Numeric value 'xyz' is not recognized</t>
         </is>
       </c>
     </row>
@@ -662,13 +606,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>TEST 7</t>
+          <t>TEST 4</t>
         </is>
       </c>
     </row>
@@ -794,98 +738,8 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TEST 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>ROW_ID</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>SUM(FACT_ORDER_ITEMS.QUANTITY)</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>COUNT(FACT_ORDERS.ORDER_ID)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TEST 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>ROW_ID</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>GROSS_REVENUE</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL_DISCOUNT</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>NET_REVENUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>15500.00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1520.00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>13980.00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A6:C6"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -898,13 +752,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>TEST 7</t>
+          <t>TEST 4</t>
         </is>
       </c>
     </row>
@@ -1030,138 +884,8 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TEST 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>ROW_ID</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>SUM(FACT_ORDER_ITEMS.QUANTITY)</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>COUNT(FACT_ORDERS.ORDER_ID)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>13980.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TEST 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>ROW_ID</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>GROSS_REVENUE</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL_DISCOUNT</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>NET_REVENUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>4000.00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4000.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>4300.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>860.00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3440.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>7200.00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>660.00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>6540.00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A6:C6"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1174,13 +898,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>TEST 7</t>
+          <t>TEST 4</t>
         </is>
       </c>
     </row>
@@ -1412,216 +1136,9 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TEST 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Row_number</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>SUM(FACT_ORDER_ITEMS.QUANTITY)</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>COUNT(FACT_ORDERS.ORDER_ID)</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SRC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>13980.00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TEST 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Row_number</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>GROSS_REVENUE</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL_DISCOUNT</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>NET_REVENUE</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>15500.00</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>1520.00</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>13980.00</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>SRC</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>4000.00</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>4000.00</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>4300.00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>860.00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3440.00</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ONLY_IN_TGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>7200.00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>660.00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>6540.00</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ONLY_IN_TGT</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_comp.xlsx
+++ b/data_comp.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,46 +506,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SELECT dim_product.PRODUCT_NAME, dim_product.BRAND, SUM(fact_order_items.QUANTITY) AS TOTAL_QTY, SUM((fact_order_items.QUANTITY * fact_order_items.UNIT_PRICE) - fact_order_items.DISCOUNT_AMOUNT) AS TOTAL_REVENUE FROM fact_order_items JOIN dim_product ON fact_order_items.PRODUCT_KEY = dim_product.PRODUCT_KEY GROUP BY dim_product.PRODUCT_NAME, dim_product.BRAND ORDER BY TOTAL_REVENUE DESC LIMIT 1;</t>
+          <t>SELECT DIM_CUSTOMER.CUSTOMER_KEY, DIM_CUSTOMER.CUSTOMER_ID, DIM_CUSTOMER.CUSTOMER_NAME, DIM_CUSTOMER.SEGMENT, DIM_GEOGRAPHY.CITY, DIM_GEOGRAPHY.STATE_REGION, DIM_GEOGRAPHY.COUNTRY FROM DIM_CUSTOMER INNER JOIN DIM_GEOGRAPHY ON DIM_CUSTOMER.GEO_KEY = DIM_GEOGRAPHY.GEO_KEY;</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SELECT PRODUCT_SALES.PRODUCT_NAME, PRODUCT_SALES.BRAND, PRODUCT_SALES.TOTAL_QTY, PRODUCT_SALES.TOTAL_REVENUE FROM PRODUCT_SALES ORDER BY PRODUCT_SALES.TOTAL_REVENUE DESC LIMIT 1;</t>
+          <t>SELECT * FROM DBT_SCHEMA.DIM_CUSTOMER_ENR;</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SELECT DIM_CUSTOMER.CUSTOMER_KEY, DIM_CUSTOMER.CUSTOMER_ID, DIM_CUSTOMER.CUSTOMER_NAME, DIM_CUSTOMER.SEGMENT, DIM_GEOGRAPHY.CITY, DIM_GEOGRAPHY.STATE_REGION, DIM_GEOGRAPHY.COUNTRY FROM DIM_CUSTOMER INNER JOIN DIM_GEOGRAPHY ON DIM_CUSTOMER.GEO_KEY = DIM_GEOGRAPHY.GEO_KEY;</t>
+          <t>SELECT c.CUSTOMER_NAME, c.SEGMENT, COUNT(DISTINCT o.ORDER_ID) AS TOTAL_ORDERS, SUM((oi.QUANTITY * oi.UNIT_PRICE) - oi.DISCOUNT_AMOUNT) AS TOTAL_SPENT FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS o JOIN DBT_POC.DBT_SCHEMA.FACT_ORDER_ITEMS oi ON o.ORDER_ID = oi.ORDER_ID JOIN DBT_POC.DBT_SCHEMA.DIM_CUSTOMER c ON o.CUSTOMER_KEY = c.CUSTOMER_KEY GROUP BY c.CUSTOMER_NAME, c.SEGMENT;</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SELECT * FROM DBT_SCHEMA.DIM_CUSTOMER_ENR;</t>
+          <t>SELECT CUSTOMER_SALES.CUSTOMER_NAME, CUSTOMER_SALES.SEGMENT, CUSTOMER_SALES.TOTAL_ORDERS, CUSTOMER_SALES.TOTAL_SPENT FROM CUSTOMER_SALES;</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SELECT c.CUSTOMER_NAME, c.SEGMENT, COUNT(DISTINCT o.ORDER_ID) AS TOTAL_ORDERS, SUM((oi.QUANTITY * oi.UNIT_PRICE) - oi.DISCOUNT_AMOUNT) AS TOTAL_SPENT FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS o JOIN DBT_POC.DBT_SCHEMA.FACT_ORDER_ITEMS oi ON o.ORDER_ID = oi.ORDER_ID JOIN DBT_POC.DBT_SCHEMA.DIM_CUSTOMER c ON o.CUSTOMER_KEY = c.CUSTOMER_KEY GROUP BY c.CUSTOMER_NAME, c.SEGMENT;</t>
+          <t>SELECT c.CUSTOMER_NAME, c.SEGMENT, COUNT(DISTINCT o.ORDER_ID) AS TOTAL_ORDERS, SUM((oi.QUANTITY * oi.UNIT_PRICE) - oi.DISCOUNT_AMOUNT) AS TOTAL_SPENT, CASE WHEN SUM((oi.QUANTITY * oi.UNIT_PRICE) - oi.DISCOUNT_AMOUNT) &gt; 1000 THEN 'HIGH' ELSE 'LOW' END AS SPENT_ FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS o JOIN DBT_POC.DBT_SCHEMA.FACT_ORDER_ITEMS oi ON o.ORDER_ID = oi.ORDER_ID JOIN DBT_POC.DBT_SCHEMA.DIM_CUSTOMER c ON o.CUSTOMER_KEY = c.CUSTOMER_KEY GROUP BY c.CUSTOMER_NAME, c.SEGMENT;</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SELECT CUSTOMER_SALES.CUSTOMER_NAME, CUSTOMER_SALES.SEGMENT, CUSTOMER_SALES.TOTAL_ORDERS, CUSTOMER_SALES.TOTAL_SPENT FROM CUSTOMER_SALES;</t>
+          <t>SELECT CUSTOMER_NAME, SEGMENT, TOTAL_ORDERS, TOTAL_SPENT, CASE WHEN TOTAL_SPENT &gt; 1000 THEN 'HIGH' ELSE 'LOW' END AS SPENT_BAND FROM DBT_SCHEMA.CUSTOMER_SALES;</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -557,39 +557,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SELECT c.CUSTOMER_NAME, c.SEGMENT, COUNT(DISTINCT o.ORDER_ID) AS TOTAL_ORDERS, SUM((oi.QUANTITY * oi.UNIT_PRICE) - oi.DISCOUNT_AMOUNT) AS TOTAL_SPENT, CASE WHEN SUM((oi.QUANTITY * oi.UNIT_PRICE) - oi.DISCOUNT_AMOUNT) &gt; 1000 THEN 'HIGH' ELSE 'LOW' END AS SPENT_BAND FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS o JOIN DBT_POC.DBT_SCHEMA.FACT_ORDER_ITEMS oi ON o.ORDER_ID = oi.ORDER_ID JOIN DBT_POC.DBT_SCHEMA.DIM_CUSTOMER c ON o.CUSTOMER_KEY = c.CUSTOMER_KEY GROUP BY c.CUSTOMER_NAME, c.SEGMENT;</t>
+          <t>SELECT SUM(oi.QUANTITY * oi.UNIT_PRICE) - SUM(oi.DISCOUNT_AMOUNT) FROM DBT_POC.DBT_SCHEMA.fact_order_items oi WHERE oi.ORDER_ID = 50003;</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SELECT CUSTOMER_NAME, SEGMENT, TOTAL_ORDERS, TOTAL_SPENT, CASE WHEN TOTAL_SPENT &gt; 1000 THEN 'HIGH' ELSE 'LOW' END AS SPENT_BAND FROM DBT_SCHEMA.CUSTOMER_SALES;</t>
+          <t>-- INVALID SQL
+-- Execution failed on sql 'SELECT SUM(ORDER_REVENUE.GROSS_REVENUE) FROM ORDER_REVENUE WHERE ORDER_REVENUE.ORDER_ID = 'xyz';': 100038 (22018): Numeric value 'xyz' is not recognized
+SELECT SUM(ORDER_REVENUE.GROSS_REVENUE) FROM ORDER_REVENUE WHERE ORDER_REVENUE.ORDER_ID = 'xyz';</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SELECT SUM(oi.QUANTITY * oi.UNIT_PRICE) - SUM(oi.DISCOUNT_AMOUNT) FROM DBT_POC.DBT_SCHEMA.fact_order_items oi WHERE oi.ORDER_ID = 50003;</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>-- INVALID SQL
--- Execution failed on sql 'SELECT SUM(oi.QUANTITY * oi.UNIT_PRICE) - SUM(oi.DISCOUNT_AMOUNT) FROM DBT_POC.DBT_SCHEMA.fact_order_items oi JOIN DBT_POC.DBT_SCHEMA.fact_orders o ON oi.ORDER_ID = o.ORDER_ID WHERE o.ORDER_ID = 'xyz';': 100038 (22018): Numeric value 'xyz' is not recognized
-SELECT SUM(oi.QUANTITY * oi.UNIT_PRICE) - SUM(oi.DISCOUNT_AMOUNT) FROM DBT_POC.DBT_SCHEMA.fact_order_items oi JOIN DBT_POC.DBT_SCHEMA.fact_orders o ON oi.ORDER_ID = o.ORDER_ID WHERE o.ORDER_ID = 'xyz';</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>100038 (22018): Numeric value 'xyz' is not recognized</t>
         </is>
@@ -612,7 +595,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>TEST 4</t>
+          <t>TEST 3</t>
         </is>
       </c>
     </row>
@@ -758,7 +741,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>TEST 4</t>
+          <t>TEST 3</t>
         </is>
       </c>
     </row>
@@ -904,7 +887,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>TEST 4</t>
+          <t>TEST 3</t>
         </is>
       </c>
     </row>

--- a/data_comp.xlsx
+++ b/data_comp.xlsx
@@ -540,7 +540,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SELECT c.CUSTOMER_NAME, c.SEGMENT, COUNT(DISTINCT o.ORDER_ID) AS TOTAL_ORDERS, SUM((oi.QUANTITY * oi.UNIT_PRICE) - oi.DISCOUNT_AMOUNT) AS TOTAL_SPENT, CASE WHEN SUM((oi.QUANTITY * oi.UNIT_PRICE) - oi.DISCOUNT_AMOUNT) &gt; 1000 THEN 'HIGH' ELSE 'LOW' END AS SPENT_ FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS o JOIN DBT_POC.DBT_SCHEMA.FACT_ORDER_ITEMS oi ON o.ORDER_ID = oi.ORDER_ID JOIN DBT_POC.DBT_SCHEMA.DIM_CUSTOMER c ON o.CUSTOMER_KEY = c.CUSTOMER_KEY GROUP BY c.CUSTOMER_NAME, c.SEGMENT;</t>
+          <t>SELECT c.CUSTOMER_NAME, c.SEGMENT, COUNT(DISTINCT o.ORDER_ID) AS TOTAL_ORDERS, SUM((oi.QUANTITY * oi.UNIT_PRICE) - oi.DISCOUNT_AMOUNT) AS TOTAL_SPENT, CASE WHEN SUM((oi.QUANTITY * oi.UNIT_PRICE) - oi.DISCOUNT_AMOUNT) &gt; 1000 THEN 'HIGH' ELSE 'LOW' END AS SPENT_BAND FROM DBT_POC.DBT_SCHEMA.FACT_ORDERS o JOIN DBT_POC.DBT_SCHEMA.FACT_ORDER_ITEMS oi ON o.ORDER_ID = oi.ORDER_ID JOIN DBT_POC.DBT_SCHEMA.DIM_CUSTOMER c ON o.CUSTOMER_KEY = c.CUSTOMER_KEY GROUP BY c.CUSTOMER_NAME, c.SEGMENT;</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,8 +563,8 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>-- INVALID SQL
--- Execution failed on sql 'SELECT SUM(ORDER_REVENUE.GROSS_REVENUE) FROM ORDER_REVENUE WHERE ORDER_REVENUE.ORDER_ID = 'xyz';': 100038 (22018): Numeric value 'xyz' is not recognized
-SELECT SUM(ORDER_REVENUE.GROSS_REVENUE) FROM ORDER_REVENUE WHERE ORDER_REVENUE.ORDER_ID = 'xyz';</t>
+-- Execution failed on sql 'SELECT SUM(oi.QUANTITY * oi.UNIT_PRICE) - SUM(oi.DISCOUNT_AMOUNT) FROM DBT_POC.DBT_SCHEMA.fact_order_items oi WHERE oi.ORDER_ID = 'xyz';': 100038 (22018): Numeric value 'xyz' is not recognized
+SELECT SUM(oi.QUANTITY * oi.UNIT_PRICE) - SUM(oi.DISCOUNT_AMOUNT) FROM DBT_POC.DBT_SCHEMA.fact_order_items oi WHERE oi.ORDER_ID = 'xyz';</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
